--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.21712</v>
+        <v>17.01673</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69536</v>
+        <v>16.28788</v>
       </c>
       <c r="E2" t="n">
-        <v>16.90466</v>
+        <v>16.91492</v>
       </c>
       <c r="F2" t="n">
-        <v>41.68416</v>
+        <v>41.3774</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05159</v>
+        <v>0.05062</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83004</v>
+        <v>1.84797</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88687</v>
+        <v>16.9127</v>
       </c>
       <c r="D3" t="n">
-        <v>16.81161</v>
+        <v>16.38228</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70165</v>
+        <v>16.58055</v>
       </c>
       <c r="F3" t="n">
-        <v>41.89993</v>
+        <v>43.09873</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05099</v>
+        <v>0.05065</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80779</v>
+        <v>1.81666</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.76864</v>
+        <v>16.65438</v>
       </c>
       <c r="D4" t="n">
-        <v>16.73896</v>
+        <v>16.5416</v>
       </c>
       <c r="E4" t="n">
-        <v>16.60573</v>
+        <v>16.64755</v>
       </c>
       <c r="F4" t="n">
-        <v>42.11012</v>
+        <v>41.52324</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04997</v>
+        <v>0.05179</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85673</v>
+        <v>1.83447</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.49736</v>
+        <v>16.73386</v>
       </c>
       <c r="D5" t="n">
-        <v>16.21329</v>
+        <v>16.50435</v>
       </c>
       <c r="E5" t="n">
-        <v>16.71576</v>
+        <v>16.6348</v>
       </c>
       <c r="F5" t="n">
-        <v>42.0962</v>
+        <v>42.28493</v>
       </c>
       <c r="G5" t="n">
         <v>0.05047</v>
       </c>
       <c r="H5" t="n">
-        <v>1.78588</v>
+        <v>1.82295</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.97028</v>
+        <v>17.17561</v>
       </c>
       <c r="D6" t="n">
-        <v>17.13755</v>
+        <v>16.58766</v>
       </c>
       <c r="E6" t="n">
-        <v>16.63633</v>
+        <v>16.82647</v>
       </c>
       <c r="F6" t="n">
-        <v>42.32811</v>
+        <v>43.08932</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05114</v>
+        <v>0.05152</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82376</v>
+        <v>1.82711</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75967</v>
+        <v>17.08461</v>
       </c>
       <c r="D7" t="n">
-        <v>16.5359</v>
+        <v>16.55067</v>
       </c>
       <c r="E7" t="n">
-        <v>16.81436</v>
+        <v>16.79114</v>
       </c>
       <c r="F7" t="n">
-        <v>42.52961</v>
+        <v>40.96096</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04973</v>
+        <v>0.05074</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82357</v>
+        <v>1.83794</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.94912</v>
+        <v>16.91994</v>
       </c>
       <c r="D8" t="n">
-        <v>16.44142</v>
+        <v>16.4456</v>
       </c>
       <c r="E8" t="n">
-        <v>16.72357</v>
+        <v>16.67605</v>
       </c>
       <c r="F8" t="n">
-        <v>42.22001</v>
+        <v>41.35962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05095</v>
+        <v>0.04931</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79514</v>
+        <v>1.82352</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.71414</v>
+        <v>16.9816</v>
       </c>
       <c r="D9" t="n">
-        <v>16.79004</v>
+        <v>16.51355</v>
       </c>
       <c r="E9" t="n">
-        <v>16.97106</v>
+        <v>16.5865</v>
       </c>
       <c r="F9" t="n">
-        <v>42.10847</v>
+        <v>42.37887</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05118</v>
+        <v>0.05023</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84857</v>
+        <v>1.82956</v>
       </c>
     </row>
     <row r="10">
@@ -660,744 +660,712 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.99546</v>
+        <v>17.26938</v>
       </c>
       <c r="D10" t="n">
-        <v>16.80332</v>
+        <v>16.60348</v>
       </c>
       <c r="E10" t="n">
-        <v>16.48518</v>
+        <v>16.75241</v>
       </c>
       <c r="F10" t="n">
-        <v>42.90817</v>
+        <v>43.56151</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05019</v>
+        <v>0.05054</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83246</v>
+        <v>1.82324</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.05384</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.65076</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.65544</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41.72616</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.81386</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.45071</v>
+        <v>16.97475</v>
       </c>
       <c r="D12" t="n">
-        <v>16.51691</v>
+        <v>16.58947</v>
       </c>
       <c r="E12" t="n">
-        <v>16.49719</v>
+        <v>16.68677</v>
       </c>
       <c r="F12" t="n">
-        <v>42.51196</v>
+        <v>41.56705</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04947</v>
+        <v>0.05122</v>
       </c>
       <c r="H12" t="n">
-        <v>1.80205</v>
+        <v>1.81159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.6428</v>
+        <v>16.86568</v>
       </c>
       <c r="D13" t="n">
-        <v>16.48279</v>
+        <v>16.4122</v>
       </c>
       <c r="E13" t="n">
-        <v>16.58631</v>
+        <v>16.63719</v>
       </c>
       <c r="F13" t="n">
-        <v>42.29468</v>
+        <v>42.74877</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05169</v>
+        <v>0.05188</v>
       </c>
       <c r="H13" t="n">
-        <v>1.82644</v>
+        <v>1.82233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.95483</v>
+        <v>16.94621</v>
       </c>
       <c r="D14" t="n">
-        <v>16.73549</v>
+        <v>16.44159</v>
       </c>
       <c r="E14" t="n">
-        <v>16.66467</v>
+        <v>16.52151</v>
       </c>
       <c r="F14" t="n">
-        <v>42.89048</v>
+        <v>42.6339</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05021</v>
+        <v>0.05053</v>
       </c>
       <c r="H14" t="n">
-        <v>1.78398</v>
+        <v>1.83637</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.87408</v>
+        <v>16.98634</v>
       </c>
       <c r="D15" t="n">
-        <v>16.91796</v>
+        <v>16.63065</v>
       </c>
       <c r="E15" t="n">
-        <v>16.66328</v>
+        <v>16.86451</v>
       </c>
       <c r="F15" t="n">
-        <v>43.19016</v>
+        <v>42.31979</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05102</v>
+        <v>0.05053</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83329</v>
+        <v>1.83462</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.92251</v>
+        <v>16.91518</v>
       </c>
       <c r="D16" t="n">
-        <v>16.76225</v>
+        <v>16.79916</v>
       </c>
       <c r="E16" t="n">
-        <v>16.82716</v>
+        <v>16.82379</v>
       </c>
       <c r="F16" t="n">
-        <v>42.80825</v>
+        <v>42.75727</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05085</v>
+        <v>0.05071</v>
       </c>
       <c r="H16" t="n">
-        <v>1.83366</v>
+        <v>1.82919</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.18122</v>
+        <v>17.04049</v>
       </c>
       <c r="D17" t="n">
-        <v>16.66672</v>
+        <v>16.51981</v>
       </c>
       <c r="E17" t="n">
-        <v>16.8186</v>
+        <v>16.95668</v>
       </c>
       <c r="F17" t="n">
-        <v>42.87313</v>
+        <v>42.38179</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04994</v>
+        <v>0.04962</v>
       </c>
       <c r="H17" t="n">
-        <v>1.78586</v>
+        <v>1.82684</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.70665</v>
+        <v>16.89552</v>
       </c>
       <c r="D18" t="n">
-        <v>16.42224</v>
+        <v>16.40611</v>
       </c>
       <c r="E18" t="n">
-        <v>16.73518</v>
+        <v>16.50925</v>
       </c>
       <c r="F18" t="n">
-        <v>42.88806</v>
+        <v>42.63315</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05078</v>
+        <v>0.04946</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86191</v>
+        <v>1.82718</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.31603</v>
+        <v>16.94549</v>
       </c>
       <c r="D19" t="n">
-        <v>16.53305</v>
+        <v>16.22579</v>
       </c>
       <c r="E19" t="n">
-        <v>16.70584</v>
+        <v>16.44858</v>
       </c>
       <c r="F19" t="n">
-        <v>42.85614</v>
+        <v>42.66779</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05061</v>
+        <v>0.05104</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84741</v>
+        <v>1.85557</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>17.09554</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.49182</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.80625</v>
-      </c>
-      <c r="F20" t="n">
-        <v>43.07721</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05085</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.79647</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.60517</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.1164</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.61682</v>
+        <v>0.61377</v>
       </c>
       <c r="D22" t="n">
-        <v>1.12486</v>
+        <v>1.12846</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.59983</v>
+        <v>0.60089</v>
       </c>
       <c r="D23" t="n">
-        <v>1.09892</v>
+        <v>1.10977</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.59954</v>
+        <v>0.60497</v>
       </c>
       <c r="D24" t="n">
-        <v>1.11921</v>
+        <v>1.1165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.60139</v>
+        <v>0.6105</v>
       </c>
       <c r="D25" t="n">
-        <v>1.12188</v>
+        <v>1.10418</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.61183</v>
+        <v>0.60462</v>
       </c>
       <c r="D26" t="n">
-        <v>1.11448</v>
+        <v>1.12838</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.6005</v>
+        <v>0.6253300000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>1.11258</v>
+        <v>1.11455</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.60619</v>
+        <v>0.61165</v>
       </c>
       <c r="D28" t="n">
-        <v>1.10752</v>
+        <v>1.12066</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.61368</v>
+        <v>0.60499</v>
       </c>
       <c r="D29" t="n">
-        <v>1.10292</v>
+        <v>1.10764</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.59905</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.1058</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.74039</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08022</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.60488</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.95216</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.10829</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09215</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12941</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.75181</v>
+        <v>0.76564</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08182</v>
+        <v>0.08097</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6119599999999999</v>
+        <v>0.60636</v>
       </c>
       <c r="F32" t="n">
-        <v>0.95787</v>
+        <v>0.97009</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11122</v>
+        <v>0.11073</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00761</v>
+        <v>0.00758</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09132</v>
+        <v>0.09109</v>
       </c>
       <c r="J32" t="n">
-        <v>0.12549</v>
+        <v>0.12971</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.76297</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08011</v>
+        <v>0.08121</v>
       </c>
       <c r="E33" t="n">
-        <v>0.60786</v>
+        <v>0.60987</v>
       </c>
       <c r="F33" t="n">
-        <v>0.97738</v>
+        <v>0.96657</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11002</v>
+        <v>0.11027</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00763</v>
+        <v>0.00755</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09173000000000001</v>
+        <v>0.09336999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0.12574</v>
+        <v>0.1276</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.74599</v>
+        <v>0.75058</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08146</v>
+        <v>0.08073</v>
       </c>
       <c r="E34" t="n">
-        <v>0.61149</v>
+        <v>0.60563</v>
       </c>
       <c r="F34" t="n">
-        <v>0.94745</v>
+        <v>0.9526</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11028</v>
+        <v>0.11066</v>
       </c>
       <c r="H34" t="n">
         <v>0.00758</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09334000000000001</v>
+        <v>0.09485</v>
       </c>
       <c r="J34" t="n">
-        <v>0.12667</v>
+        <v>0.12438</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.74978</v>
+        <v>0.76242</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08037</v>
+        <v>0.08064</v>
       </c>
       <c r="E35" t="n">
-        <v>0.60922</v>
+        <v>0.60282</v>
       </c>
       <c r="F35" t="n">
-        <v>0.95767</v>
+        <v>0.96402</v>
       </c>
       <c r="G35" t="n">
-        <v>0.11009</v>
+        <v>0.10997</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0075</v>
+        <v>0.00749</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09266000000000001</v>
+        <v>0.09233</v>
       </c>
       <c r="J35" t="n">
-        <v>0.12535</v>
+        <v>0.12444</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.74043</v>
+        <v>0.7595</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08074000000000001</v>
+        <v>0.08201</v>
       </c>
       <c r="E36" t="n">
-        <v>0.61121</v>
+        <v>0.6208</v>
       </c>
       <c r="F36" t="n">
-        <v>0.96389</v>
+        <v>0.98195</v>
       </c>
       <c r="G36" t="n">
-        <v>0.10786</v>
+        <v>0.11018</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00756</v>
+        <v>0.00757</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09349</v>
+        <v>0.09157</v>
       </c>
       <c r="J36" t="n">
-        <v>0.12696</v>
+        <v>0.12425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.74886</v>
+        <v>0.73628</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08098</v>
+        <v>0.08054</v>
       </c>
       <c r="E37" t="n">
-        <v>0.60017</v>
+        <v>0.6129</v>
       </c>
       <c r="F37" t="n">
-        <v>0.95604</v>
+        <v>0.96207</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11005</v>
+        <v>0.10943</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00758</v>
+        <v>0.00762</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09209000000000001</v>
+        <v>0.09257</v>
       </c>
       <c r="J37" t="n">
-        <v>0.12455</v>
+        <v>0.12646</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7419</v>
+        <v>0.75849</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08074000000000001</v>
+        <v>0.08098</v>
       </c>
       <c r="E38" t="n">
-        <v>0.61231</v>
+        <v>0.60145</v>
       </c>
       <c r="F38" t="n">
-        <v>0.97138</v>
+        <v>0.9659799999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1116</v>
+        <v>0.10826</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00752</v>
+        <v>0.0076</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09343</v>
+        <v>0.09213</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12669</v>
+        <v>0.1266</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.7522</v>
+        <v>0.75604</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08214</v>
+        <v>0.08056000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>0.60826</v>
+        <v>0.60645</v>
       </c>
       <c r="F39" t="n">
-        <v>0.95298</v>
+        <v>0.97916</v>
       </c>
       <c r="G39" t="n">
-        <v>0.10909</v>
+        <v>0.10782</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00752</v>
+        <v>0.00743</v>
       </c>
       <c r="I39" t="n">
-        <v>0.093</v>
+        <v>0.09225999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>0.12626</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.73321</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.07902000000000001</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.60377</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.9571499999999999</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.10964</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.09249</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.12641</v>
+        <v>0.12496</v>
       </c>
     </row>
   </sheetData>
